--- a/addons/sale/static/xls/quotations_import_template.xlsx
+++ b/addons/sale/static/xls/quotations_import_template.xlsx
@@ -106,7 +106,7 @@
     <t xml:space="preserve">S00003</t>
   </si>
   <si>
-    <t xml:space="preserve">Deco Addict</t>
+    <t xml:space="preserve">Acme Corporation</t>
   </si>
   <si>
     <t xml:space="preserve">15 Days</t>
